--- a/gdlearn/스타레일_광추 시스템 데이터테이블_스킬구조개선_v3.xlsx
+++ b/gdlearn/스타레일_광추 시스템 데이터테이블_스킬구조개선_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gdlearn\gdlearn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38C303B-47A6-4575-B839-BE164134C644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BC7261-0971-4873-934D-4F2279E6CB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="1367">
   <si>
     <t>광추 레벨업 경험치 곡선 테이블</t>
   </si>
@@ -4240,7 +4240,11 @@
     <t>배포 전 참조 무결성 검사</t>
   </si>
   <si>
-    <t>피의 불꽃이여, 앞길을 태우던가</t>
+    <t>피의 불꽃이여, 앞길을 태워라</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>LC_1011</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5225,7 +5229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -5917,6 +5921,62 @@
         <v>1000</v>
       </c>
       <c r="R14" s="9" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="216">
+      <c r="A15" s="9" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>997</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="E15" s="9">
+        <v>6</v>
+      </c>
+      <c r="F15" s="9">
+        <v>5</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>998</v>
+      </c>
+      <c r="I15" s="9">
+        <v>23042</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>986</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>999</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="N15" s="9">
+        <v>9999</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="R15" s="9" t="s">
         <v>1001</v>
       </c>
     </row>
